--- a/문서/Monster/MonsterData.xlsx
+++ b/문서/Monster/MonsterData.xlsx
@@ -1110,6 +1110,21 @@
       <c r="B2" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="C2" s="1">
+        <v>50</v>
+      </c>
+      <c r="D2" s="1">
+        <v>50</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>7</v>
+      </c>
+      <c r="G2" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1">
@@ -1117,6 +1132,21 @@
       </c>
       <c r="B3" s="1" t="s">
         <v>39</v>
+      </c>
+      <c r="C3" s="1">
+        <v>250</v>
+      </c>
+      <c r="D3" s="1">
+        <v>250</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F3" s="1">
+        <v>15</v>
+      </c>
+      <c r="G3" s="1">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
